--- a/artfynd/A 2579-2025 artfynd.xlsx
+++ b/artfynd/A 2579-2025 artfynd.xlsx
@@ -886,7 +886,7 @@
         <v>121539639</v>
       </c>
       <c r="B4" t="n">
-        <v>57159</v>
+        <v>57277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 2579-2025 artfynd.xlsx
+++ b/artfynd/A 2579-2025 artfynd.xlsx
@@ -886,7 +886,7 @@
         <v>121539639</v>
       </c>
       <c r="B4" t="n">
-        <v>57277</v>
+        <v>57159</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
